--- a/assets/constructions/examples/ctd_tsmb_tupleturn.xlsx
+++ b/assets/constructions/examples/ctd_tsmb_tupleturn.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ctd" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ctd" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL6"/>
+  <dimension ref="A1:AQ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -619,11 +619,36 @@
           <t>releasepack</t>
         </is>
       </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>lcs</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>pricecurrency</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue_rub</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>4.0SIR1.1SD472-1.1VMX</t>
+          <t>6.0SIR0.2M-Bore-1VMX</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -633,7 +658,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Microscope</t>
+          <t>Micro</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -642,39 +667,47 @@
         </is>
       </c>
       <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>VAR_6SI02</t>
+        </is>
+      </c>
       <c r="G2" t="inlineStr">
         <is>
           <t>VARGUS</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>4.1</v>
+        <v>6.2</v>
       </c>
       <c r="I2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
+        <v>6</v>
+      </c>
+      <c r="J2" t="n">
+        <v>6</v>
+      </c>
+      <c r="K2" t="n">
+        <v>6</v>
+      </c>
       <c r="L2" t="n">
-        <v>1.9</v>
+        <v>2.92</v>
       </c>
       <c r="M2" t="n">
-        <v>1.4</v>
+        <v>0.77</v>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="P2" t="n">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="n">
-        <v>1.1</v>
+        <v>0.77</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -690,7 +723,7 @@
       <c r="AA2" t="inlineStr"/>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>VARGUS_4SI02</t>
+          <t>VARGUS_6SI02</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -700,12 +733,12 @@
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>VMX</t>
+          <t>VBX</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>TiN</t>
+          <t>TiCN</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr"/>
@@ -714,11 +747,7 @@
           <t>VHM</t>
         </is>
       </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>DIN 472</t>
-        </is>
-      </c>
+      <c r="AH2" t="inlineStr"/>
       <c r="AI2" t="n">
         <v>0</v>
       </c>
@@ -728,14 +757,25 @@
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>Full MAIN VARDEX 2022-METRIC.pdf</t>
+          <t>2018/VARGUS 2018 General Catalog</t>
+        </is>
+      </c>
+      <c r="AM2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AN2" t="inlineStr"/>
+      <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="inlineStr"/>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>PMKNSH</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>8.0SIR1.10M-D472-2.0VMX</t>
+          <t>8.0SIR1.3M-D472-2.0VMX</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -843,11 +883,30 @@
           <t>Full MAIN VARDEX 2022-METRIC.pdf</t>
         </is>
       </c>
+      <c r="AM3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>124.1</v>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AP3" t="n">
+        <v>11408.97</v>
+      </c>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>PMKNSH</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>10.0SIR1.60M-D472-3.5VMX</t>
+          <t>6.0SIR1.6MD472-1.5VMX</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -873,29 +932,29 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>10.4</v>
+        <v>6.1</v>
       </c>
       <c r="I4" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="n">
-        <v>4.9</v>
+        <v>2.9</v>
       </c>
       <c r="M4" t="n">
-        <v>4</v>
+        <v>1.8</v>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="P4" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="n">
-        <v>3.5</v>
+        <v>1.5</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -914,7 +973,7 @@
       <c r="AA4" t="inlineStr"/>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>VARGUS_10SI02</t>
+          <t>VARGUS_6SI02</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -953,13 +1012,32 @@
       <c r="AL4" t="inlineStr">
         <is>
           <t>Full MAIN VARDEX 2022-METRIC.pdf</t>
+        </is>
+      </c>
+      <c r="AM4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>77.55</v>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AP4" t="n">
+        <v>7129.46</v>
+      </c>
+      <c r="AQ4" t="inlineStr">
+        <is>
+          <t>PMKNSH</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>8.0SIR0.2M-BORE-1VMX</t>
+          <t>6.0SIR1.3MD472-1.5VMX</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -969,7 +1047,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Micro</t>
+          <t>Microscope</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -978,47 +1056,39 @@
         </is>
       </c>
       <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>VAR_8SI02</t>
-        </is>
-      </c>
+      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
           <t>VARGUS</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>8.199999999999999</v>
+        <v>6.1</v>
       </c>
       <c r="I5" t="n">
-        <v>8</v>
-      </c>
-      <c r="J5" t="n">
-        <v>8</v>
-      </c>
-      <c r="K5" t="n">
-        <v>8</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
       <c r="L5" t="n">
-        <v>3.92</v>
+        <v>2.9</v>
       </c>
       <c r="M5" t="n">
-        <v>0.82</v>
+        <v>1.8</v>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="P5" t="n">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="n">
-        <v>0.82</v>
+        <v>1.5</v>
       </c>
       <c r="S5" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1034,7 +1104,7 @@
       <c r="AA5" t="inlineStr"/>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>VARGUS_8SI02</t>
+          <t>VARGUS_6SI02</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1044,12 +1114,12 @@
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>VBX</t>
+          <t>VMX</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>TiCN</t>
+          <t>TiN</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr"/>
@@ -1058,7 +1128,11 @@
           <t>VHM</t>
         </is>
       </c>
-      <c r="AH5" t="inlineStr"/>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>DIN 472</t>
+        </is>
+      </c>
       <c r="AI5" t="n">
         <v>0</v>
       </c>
@@ -1068,14 +1142,33 @@
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>2018/VARGUS 2018 General Catalog</t>
+          <t>Full MAIN VARDEX 2022-METRIC.pdf</t>
+        </is>
+      </c>
+      <c r="AM5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>77.55</v>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AP5" t="n">
+        <v>7129.46</v>
+      </c>
+      <c r="AQ5" t="inlineStr">
+        <is>
+          <t>PMKNSH</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>3.0SIR0.1S-BORE-1VMX</t>
+          <t>6.0SIR1.85SD472-1.5VMX</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1085,7 +1178,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Micro</t>
+          <t>Microscope</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1094,33 +1187,25 @@
         </is>
       </c>
       <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>VAR_3SI01</t>
-        </is>
-      </c>
+      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
           <t>VARGUS</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>3.2</v>
+        <v>6.1</v>
       </c>
       <c r="I6" t="n">
-        <v>3</v>
-      </c>
-      <c r="J6" t="n">
-        <v>3</v>
-      </c>
-      <c r="K6" t="n">
-        <v>3</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
       <c r="L6" t="n">
-        <v>1.36</v>
+        <v>2.9</v>
       </c>
       <c r="M6" t="n">
-        <v>0.5600000000000001</v>
+        <v>1.8</v>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="n">
@@ -1131,10 +1216,10 @@
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="n">
-        <v>0.5600000000000001</v>
+        <v>1.5</v>
       </c>
       <c r="S6" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1150,7 +1235,7 @@
       <c r="AA6" t="inlineStr"/>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>VARGUS_3SI01</t>
+          <t>VARGUS_6SI02</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1160,12 +1245,12 @@
       </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>VTX</t>
+          <t>VMX</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>TiAlN</t>
+          <t>TiN</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr"/>
@@ -1174,7 +1259,11 @@
           <t>VHM</t>
         </is>
       </c>
-      <c r="AH6" t="inlineStr"/>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>DIN 472</t>
+        </is>
+      </c>
       <c r="AI6" t="n">
         <v>0</v>
       </c>
@@ -1184,7 +1273,18 @@
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>2018/VARGUS 2018 General Catalog</t>
+          <t>Full MAIN VARDEX 2022-METRIC.pdf</t>
+        </is>
+      </c>
+      <c r="AM6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN6" t="inlineStr"/>
+      <c r="AO6" t="inlineStr"/>
+      <c r="AP6" t="inlineStr"/>
+      <c r="AQ6" t="inlineStr">
+        <is>
+          <t>PMKNSH</t>
         </is>
       </c>
     </row>
